--- a/data/trans_dic/P1001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,1</t>
+          <t>9,04; 13,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 15,58</t>
+          <t>11,2; 15,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,57</t>
+          <t>7,14; 11,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,56</t>
+          <t>9,5; 14,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 15,57</t>
+          <t>11,87; 15,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,82; 26,72</t>
+          <t>21,66; 26,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,49</t>
+          <t>20,13; 25,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,94; 25,59</t>
+          <t>20,81; 25,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,83</t>
+          <t>11,22; 14,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 21,17</t>
+          <t>17,9; 21,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,01</t>
+          <t>15,15; 18,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,92; 20,51</t>
+          <t>16,71; 20,42</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,67</t>
+          <t>2,76; 4,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 5,71</t>
+          <t>3,68; 5,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,84</t>
+          <t>4,76; 6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,07</t>
+          <t>3,25; 6,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,44</t>
+          <t>5,83; 8,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,41</t>
+          <t>8,41; 11,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,95</t>
+          <t>7,41; 10,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,13</t>
+          <t>5,84; 9,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,06</t>
+          <t>4,54; 6,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 8,28</t>
+          <t>6,24; 7,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,1</t>
+          <t>6,36; 8,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 7,18</t>
+          <t>5,06; 7,27</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,01</t>
+          <t>2,53; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,66</t>
+          <t>2,81; 8,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,69</t>
+          <t>1,7; 4,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,01</t>
+          <t>2,72; 5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,16</t>
+          <t>3,66; 8,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,64</t>
+          <t>3,44; 7,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,54</t>
+          <t>4,35; 8,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,53</t>
+          <t>5,57; 9,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,29</t>
+          <t>3,61; 6,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,96</t>
+          <t>3,59; 6,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,99</t>
+          <t>3,46; 6,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,19</t>
+          <t>4,51; 7,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,87</t>
+          <t>5,25; 6,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,16</t>
+          <t>6,25; 8,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,94</t>
+          <t>5,4; 7,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,76</t>
+          <t>4,38; 6,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,5</t>
+          <t>8,45; 10,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,48; 15,91</t>
+          <t>13,54; 15,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 13,38</t>
+          <t>11,2; 13,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,85; 12,06</t>
+          <t>8,89; 12,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,42</t>
+          <t>7,14; 8,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 11,66</t>
+          <t>10,16; 11,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 10,02</t>
+          <t>8,54; 9,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,07</t>
+          <t>7,25; 9,19</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95512; 135153</t>
+          <t>93297; 135136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106074; 151873</t>
+          <t>109113; 152713</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55068; 87249</t>
+          <t>53846; 87130</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48174; 74863</t>
+          <t>48879; 74567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>156250; 204794</t>
+          <t>156122; 205331</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>291723; 357134</t>
+          <t>289585; 357688</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>197551; 253529</t>
+          <t>200192; 255834</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>157943; 193006</t>
+          <t>156915; 195857</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263600; 324681</t>
+          <t>263420; 329422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>411899; 489247</t>
+          <t>413747; 488767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>263879; 332481</t>
+          <t>265000; 326018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>214577; 260210</t>
+          <t>212004; 259040</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46752; 79070</t>
+          <t>46735; 77423</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73778; 112123</t>
+          <t>72213; 113564</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99520; 142010</t>
+          <t>98913; 143584</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74896; 138949</t>
+          <t>74464; 141154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92940; 133930</t>
+          <t>92555; 133535</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147992; 200492</t>
+          <t>147808; 202334</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148309; 197868</t>
+          <t>147243; 199260</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>122674; 204257</t>
+          <t>130720; 205083</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>144809; 198758</t>
+          <t>148873; 199448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236548; 307990</t>
+          <t>232188; 297034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260622; 329173</t>
+          <t>258653; 325256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>226628; 325234</t>
+          <t>229267; 329258</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14060; 33138</t>
+          <t>13960; 34163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13355; 36872</t>
+          <t>13503; 38650</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9290; 25674</t>
+          <t>9297; 26728</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17609; 38880</t>
+          <t>17565; 38679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18688; 38856</t>
+          <t>17446; 38736</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14875; 35044</t>
+          <t>15787; 35816</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23448; 46920</t>
+          <t>23905; 46220</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37807; 62915</t>
+          <t>36812; 61212</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36178; 64637</t>
+          <t>37054; 63802</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33427; 65374</t>
+          <t>33695; 64003</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36472; 65641</t>
+          <t>37893; 66777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59555; 94018</t>
+          <t>58932; 93178</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172453; 225005</t>
+          <t>171962; 228714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>211850; 278792</t>
+          <t>213584; 273735</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>177812; 234416</t>
+          <t>182458; 238346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153165; 233381</t>
+          <t>151143; 231047</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>283244; 354868</t>
+          <t>285475; 353205</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>478911; 565466</t>
+          <t>481085; 567568</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>390957; 472695</t>
+          <t>395525; 476170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>323227; 440262</t>
+          <t>324541; 439659</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>472859; 560462</t>
+          <t>475327; 557935</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>704252; 812700</t>
+          <t>707927; 818191</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>590009; 692303</t>
+          <t>589825; 690164</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>509052; 644092</t>
+          <t>515094; 652771</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1001-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,1</t>
+          <t>9,35; 13,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,2; 15,67</t>
+          <t>11,18; 15,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 11,55</t>
+          <t>7,3; 11,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 14,5</t>
+          <t>8,96; 13,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 15,61</t>
+          <t>11,68; 15,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,66; 26,76</t>
+          <t>21,88; 26,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,13; 25,72</t>
+          <t>20,06; 25,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 25,97</t>
+          <t>20,58; 25,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 14,04</t>
+          <t>11,21; 13,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 21,15</t>
+          <t>17,88; 21,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,15; 18,64</t>
+          <t>15,0; 18,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,71; 20,42</t>
+          <t>16,43; 19,88</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,57</t>
+          <t>2,78; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,79</t>
+          <t>3,69; 5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,92</t>
+          <t>4,76; 6,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,16</t>
+          <t>4,42; 6,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,41</t>
+          <t>5,85; 8,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,51</t>
+          <t>8,47; 11,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 10,02</t>
+          <t>7,34; 9,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,17</t>
+          <t>7,81; 10,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,08</t>
+          <t>4,52; 6,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,99</t>
+          <t>6,24; 8,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,36; 8,0</t>
+          <t>6,39; 8,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,27</t>
+          <t>6,39; 8,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,2</t>
+          <t>2,57; 6,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,03</t>
+          <t>2,71; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,89</t>
+          <t>1,74; 4,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,98</t>
+          <t>2,61; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,13</t>
+          <t>3,83; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,81</t>
+          <t>3,3; 7,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,42</t>
+          <t>4,12; 8,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,27</t>
+          <t>6,05; 9,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,21</t>
+          <t>3,62; 6,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,81</t>
+          <t>3,44; 6,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,09</t>
+          <t>3,35; 5,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,13</t>
+          <t>4,76; 7,19</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,98</t>
+          <t>5,25; 6,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,01</t>
+          <t>6,19; 7,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,06</t>
+          <t>5,31; 7,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,7</t>
+          <t>5,3; 6,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,45</t>
+          <t>8,41; 10,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,97</t>
+          <t>13,45; 15,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,48</t>
+          <t>11,16; 13,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,04</t>
+          <t>10,9; 12,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,38</t>
+          <t>7,11; 8,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,74</t>
+          <t>10,11; 11,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,54; 9,99</t>
+          <t>8,55; 9,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,19</t>
+          <t>8,33; 9,58</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>64598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>175007</t>
+          <t>187015</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>251613</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93297; 135136</t>
+          <t>96501; 138261</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109113; 152713</t>
+          <t>108970; 153646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53846; 87130</t>
+          <t>55099; 86357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48879; 74567</t>
+          <t>51764; 78654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>156122; 205331</t>
+          <t>153615; 206065</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>289585; 357688</t>
+          <t>292423; 356225</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>200192; 255834</t>
+          <t>199479; 255700</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>156915; 195857</t>
+          <t>168842; 207162</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>263420; 329422</t>
+          <t>263011; 325284</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413747; 488767</t>
+          <t>413365; 491920</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>265000; 326018</t>
+          <t>262286; 329901</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>212004; 259040</t>
+          <t>229826; 277958</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111510</t>
+          <t>118828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>170216</t>
+          <t>193182</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>281726</t>
+          <t>312010</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46735; 77423</t>
+          <t>47097; 77595</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72213; 113564</t>
+          <t>72331; 111937</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98913; 143584</t>
+          <t>98820; 143493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74464; 141154</t>
+          <t>98567; 147761</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92555; 133535</t>
+          <t>92855; 132480</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147808; 202334</t>
+          <t>148849; 200720</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>147243; 199260</t>
+          <t>145920; 197129</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>130720; 205083</t>
+          <t>169556; 217419</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>148873; 199448</t>
+          <t>148264; 201695</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232188; 297034</t>
+          <t>232241; 298278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258653; 325256</t>
+          <t>259542; 329476</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>229267; 329258</t>
+          <t>281289; 352463</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26591</t>
+          <t>28815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48552</t>
+          <t>56420</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75143</t>
+          <t>85235</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13960; 34163</t>
+          <t>14161; 33328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13503; 38650</t>
+          <t>13062; 35837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9297; 26728</t>
+          <t>9491; 26828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17565; 38679</t>
+          <t>18557; 41289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17446; 38736</t>
+          <t>18244; 37983</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15787; 35816</t>
+          <t>15119; 35810</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23905; 46220</t>
+          <t>22631; 45765</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36812; 61212</t>
+          <t>44430; 71706</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37054; 63802</t>
+          <t>37250; 67248</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33695; 64003</t>
+          <t>32374; 62229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37893; 66777</t>
+          <t>36728; 64534</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58932; 93178</t>
+          <t>68908; 103939</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198288</t>
+          <t>212241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>393775</t>
+          <t>436617</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>592063</t>
+          <t>648858</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>171962; 228714</t>
+          <t>171921; 227118</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>213584; 273735</t>
+          <t>211548; 271732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>182458; 238346</t>
+          <t>179380; 237131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>151143; 231047</t>
+          <t>186468; 245083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>285475; 353205</t>
+          <t>284255; 353412</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>481085; 567568</t>
+          <t>477990; 567428</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>395525; 476170</t>
+          <t>394144; 476102</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>324541; 439659</t>
+          <t>405941; 471653</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475327; 557935</t>
+          <t>473518; 564186</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>707927; 818191</t>
+          <t>704765; 814975</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>589825; 690164</t>
+          <t>591038; 685223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>515094; 652771</t>
+          <t>603563; 693962</t>
         </is>
       </c>
     </row>
